--- a/Result/profitability/3583.xlsx
+++ b/Result/profitability/3583.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM67"/>
+  <dimension ref="A1:AM68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.87625</v>
+        <v>3.1275</v>
       </c>
       <c r="N2" t="n">
-        <v>32.7625</v>
+        <v>33.3525</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.07</v>
       </c>
       <c r="M3" t="n">
-        <v>2.635</v>
+        <v>2.8725</v>
       </c>
       <c r="N3" t="n">
-        <v>31.705</v>
+        <v>33.13375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.98</v>
       </c>
       <c r="M4" t="n">
-        <v>2.12375</v>
+        <v>2.35</v>
       </c>
       <c r="N4" t="n">
-        <v>30.73875</v>
+        <v>31.805</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,13 +1018,13 @@
         <v>1.78</v>
       </c>
       <c r="M5" t="n">
-        <v>1.94625</v>
+        <v>2.21625</v>
       </c>
       <c r="N5" t="n">
-        <v>31.21375</v>
+        <v>32.11375</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.95</v>
       </c>
       <c r="M6" t="n">
-        <v>1.34625</v>
+        <v>1.515</v>
       </c>
       <c r="N6" t="n">
-        <v>29.38125</v>
+        <v>30.39875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>2.04</v>
       </c>
       <c r="M7" t="n">
-        <v>1.14375</v>
+        <v>1.2575</v>
       </c>
       <c r="N7" t="n">
-        <v>28.56625</v>
+        <v>28.95875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -8937,6 +8937,133 @@
       </c>
       <c r="AM67" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2995</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1789</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1206</v>
+      </c>
+      <c r="F68" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="G68" t="n">
+        <v>503</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>16.81%</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>13</v>
+      </c>
+      <c r="J68" t="n">
+        <v>517</v>
+      </c>
+      <c r="K68" t="n">
+        <v>406</v>
+      </c>
+      <c r="L68" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="M68" t="n">
+        <v>3.63375</v>
+      </c>
+      <c r="N68" t="n">
+        <v>34.02124999999999</v>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>1</v>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
+      </c>
+      <c r="V68" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0.8700000000000001</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0.2101449275362319</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>6.670000000000002</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.1986301369863015</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0.7578947368421052</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>7.200000000000003</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0.2178517397881998</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK68" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
